--- a/Experiment 1/Time_for_Bac_Fix_Pos50_Start.xlsx
+++ b/Experiment 1/Time_for_Bac_Fix_Pos50_Start.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Experiment 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0D9E2D1-CC30-42C8-967F-99D62A9EDCE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B14A23E-9EC9-40E6-B8F6-ACEFAA4C0BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="18675" windowHeight="12975" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="18675" windowHeight="12975" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
   </bookViews>
   <sheets>
     <sheet name="All Time Distributions" sheetId="2" r:id="rId1"/>
-    <sheet name="No Conj" sheetId="1" r:id="rId2"/>
-    <sheet name="No R_a No Conj" sheetId="3" r:id="rId3"/>
+    <sheet name="Normal Equation" sheetId="4" r:id="rId2"/>
+    <sheet name="No Conj" sheetId="1" r:id="rId3"/>
+    <sheet name="No R_a No Conj" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="7">
   <si>
     <t>Time_s</t>
   </si>
@@ -408,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E58A8867-CC7B-4A27-95B2-91AB61F5580A}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
@@ -432,6 +433,9 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1640</v>
+      </c>
       <c r="B2">
         <v>8389</v>
       </c>
@@ -440,6 +444,9 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>6705</v>
+      </c>
       <c r="B3">
         <v>10295</v>
       </c>
@@ -448,6 +455,9 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>13588</v>
+      </c>
       <c r="B4">
         <v>3898</v>
       </c>
@@ -456,6 +466,9 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>5143</v>
+      </c>
       <c r="B5">
         <v>6651</v>
       </c>
@@ -464,6 +477,9 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>6589</v>
+      </c>
       <c r="B6">
         <v>6044</v>
       </c>
@@ -472,6 +488,9 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>8560</v>
+      </c>
       <c r="B7">
         <v>8004</v>
       </c>
@@ -480,6 +499,9 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>4867</v>
+      </c>
       <c r="B8">
         <v>20570</v>
       </c>
@@ -488,6 +510,9 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>9413</v>
+      </c>
       <c r="B9">
         <v>1975</v>
       </c>
@@ -496,6 +521,9 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>4063</v>
+      </c>
       <c r="B10">
         <v>8326</v>
       </c>
@@ -504,6 +532,9 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>5341</v>
+      </c>
       <c r="B11">
         <v>8002</v>
       </c>
@@ -512,6 +543,9 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>6794</v>
+      </c>
       <c r="B12">
         <v>4867</v>
       </c>
@@ -520,6 +554,9 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>3301</v>
+      </c>
       <c r="B13">
         <v>17082</v>
       </c>
@@ -528,6 +565,9 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>10505</v>
+      </c>
       <c r="B14">
         <v>5334</v>
       </c>
@@ -536,6 +576,9 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>6398</v>
+      </c>
       <c r="B15">
         <v>5393</v>
       </c>
@@ -544,6 +587,9 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>4081</v>
+      </c>
       <c r="B16">
         <v>3162</v>
       </c>
@@ -551,7 +597,10 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>11264</v>
+      </c>
       <c r="B17">
         <v>2466</v>
       </c>
@@ -559,7 +608,10 @@
         <v>4210</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>5392</v>
+      </c>
       <c r="B18">
         <v>15678</v>
       </c>
@@ -567,7 +619,10 @@
         <v>4652</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>11935</v>
+      </c>
       <c r="B19">
         <v>5932</v>
       </c>
@@ -575,7 +630,10 @@
         <v>5145</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>8032</v>
+      </c>
       <c r="B20">
         <v>2315</v>
       </c>
@@ -583,12 +641,165 @@
         <v>4870</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>5058</v>
+      </c>
       <c r="B21">
         <v>1351</v>
       </c>
       <c r="D21">
         <v>4288</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>17146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>3574</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>4616</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>6972</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>19492</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>14856</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>7890</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>5025</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29157</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>6848</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>8353</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>7072</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>5740</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>4602</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>3289</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>3033</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>4978</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>6970</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>15991</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>13533</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>3040</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>10768</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>4817</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>8986</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>4026</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>10060</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>3175</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>3427</v>
       </c>
     </row>
   </sheetData>
@@ -597,6 +808,581 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14A4F54D-F9A8-4A57-B36F-2ADC46C86094}">
+  <dimension ref="A1:C51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1640</v>
+      </c>
+      <c r="B2">
+        <v>27.333333333333332</v>
+      </c>
+      <c r="C2">
+        <v>0.45555555555555555</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>6705</v>
+      </c>
+      <c r="B3">
+        <v>111.75</v>
+      </c>
+      <c r="C3">
+        <v>1.8625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>13588</v>
+      </c>
+      <c r="B4">
+        <v>226.46666666666667</v>
+      </c>
+      <c r="C4">
+        <v>3.7744444444444443</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>5143</v>
+      </c>
+      <c r="B5">
+        <v>85.716666666666669</v>
+      </c>
+      <c r="C5">
+        <v>1.4286111111111111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>6589</v>
+      </c>
+      <c r="B6">
+        <v>109.81666666666666</v>
+      </c>
+      <c r="C6">
+        <v>1.8302777777777777</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>8560</v>
+      </c>
+      <c r="B7">
+        <v>142.66666666666666</v>
+      </c>
+      <c r="C7">
+        <v>2.3777777777777778</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>4867</v>
+      </c>
+      <c r="B8">
+        <v>81.11666666666666</v>
+      </c>
+      <c r="C8">
+        <v>1.3519444444444444</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>9413</v>
+      </c>
+      <c r="B9">
+        <v>156.88333333333333</v>
+      </c>
+      <c r="C9">
+        <v>2.6147222222222224</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>4063</v>
+      </c>
+      <c r="B10">
+        <v>67.716666666666669</v>
+      </c>
+      <c r="C10">
+        <v>1.128611111111111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>5341</v>
+      </c>
+      <c r="B11">
+        <v>89.016666666666666</v>
+      </c>
+      <c r="C11">
+        <v>1.4836111111111112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>6794</v>
+      </c>
+      <c r="B12">
+        <v>113.23333333333333</v>
+      </c>
+      <c r="C12">
+        <v>1.8872222222222221</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>3301</v>
+      </c>
+      <c r="B13">
+        <v>55.016666666666666</v>
+      </c>
+      <c r="C13">
+        <v>0.91694444444444445</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>10505</v>
+      </c>
+      <c r="B14">
+        <v>175.08333333333334</v>
+      </c>
+      <c r="C14">
+        <v>2.9180555555555556</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>6398</v>
+      </c>
+      <c r="B15">
+        <v>106.63333333333334</v>
+      </c>
+      <c r="C15">
+        <v>1.7772222222222223</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>4081</v>
+      </c>
+      <c r="B16">
+        <v>68.016666666666666</v>
+      </c>
+      <c r="C16">
+        <v>1.1336111111111111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>11264</v>
+      </c>
+      <c r="B17">
+        <v>187.73333333333332</v>
+      </c>
+      <c r="C17">
+        <v>3.1288888888888891</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>5392</v>
+      </c>
+      <c r="B18">
+        <v>89.86666666666666</v>
+      </c>
+      <c r="C18">
+        <v>1.4977777777777779</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>11935</v>
+      </c>
+      <c r="B19">
+        <v>198.91666666666666</v>
+      </c>
+      <c r="C19">
+        <v>3.3152777777777778</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>8032</v>
+      </c>
+      <c r="B20">
+        <v>133.86666666666667</v>
+      </c>
+      <c r="C20">
+        <v>2.2311111111111113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>5058</v>
+      </c>
+      <c r="B21">
+        <v>84.3</v>
+      </c>
+      <c r="C21">
+        <v>1.405</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>17146</v>
+      </c>
+      <c r="B22">
+        <v>285.76666666666665</v>
+      </c>
+      <c r="C22">
+        <v>4.762777777777778</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>3574</v>
+      </c>
+      <c r="B23">
+        <v>59.56666666666667</v>
+      </c>
+      <c r="C23">
+        <v>0.99277777777777776</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>4616</v>
+      </c>
+      <c r="B24">
+        <v>76.933333333333337</v>
+      </c>
+      <c r="C24">
+        <v>1.2822222222222222</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>6972</v>
+      </c>
+      <c r="B25">
+        <v>116.2</v>
+      </c>
+      <c r="C25">
+        <v>1.9366666666666668</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>19492</v>
+      </c>
+      <c r="B26">
+        <v>324.86666666666667</v>
+      </c>
+      <c r="C26">
+        <v>5.4144444444444444</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>14856</v>
+      </c>
+      <c r="B27">
+        <v>247.6</v>
+      </c>
+      <c r="C27">
+        <v>4.1266666666666669</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>7890</v>
+      </c>
+      <c r="B28">
+        <v>131.5</v>
+      </c>
+      <c r="C28">
+        <v>2.1916666666666669</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>5025</v>
+      </c>
+      <c r="B29">
+        <v>83.75</v>
+      </c>
+      <c r="C29">
+        <v>1.3958333333333333</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29157</v>
+      </c>
+      <c r="B30">
+        <v>485.95</v>
+      </c>
+      <c r="C30">
+        <v>8.0991666666666671</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>6848</v>
+      </c>
+      <c r="B31">
+        <v>114.13333333333334</v>
+      </c>
+      <c r="C31">
+        <v>1.9022222222222223</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>8353</v>
+      </c>
+      <c r="B32">
+        <v>139.21666666666667</v>
+      </c>
+      <c r="C32">
+        <v>2.3202777777777777</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>7072</v>
+      </c>
+      <c r="B33">
+        <v>117.86666666666666</v>
+      </c>
+      <c r="C33">
+        <v>1.9644444444444444</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>5740</v>
+      </c>
+      <c r="B34">
+        <v>95.666666666666671</v>
+      </c>
+      <c r="C34">
+        <v>1.5944444444444446</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>4602</v>
+      </c>
+      <c r="B35">
+        <v>76.7</v>
+      </c>
+      <c r="C35">
+        <v>1.2783333333333333</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>3289</v>
+      </c>
+      <c r="B36">
+        <v>54.81666666666667</v>
+      </c>
+      <c r="C36">
+        <v>0.91361111111111115</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>3033</v>
+      </c>
+      <c r="B37">
+        <v>50.55</v>
+      </c>
+      <c r="C37">
+        <v>0.84250000000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>4978</v>
+      </c>
+      <c r="B38">
+        <v>82.966666666666669</v>
+      </c>
+      <c r="C38">
+        <v>1.3827777777777779</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>6970</v>
+      </c>
+      <c r="B39">
+        <v>116.16666666666667</v>
+      </c>
+      <c r="C39">
+        <v>1.9361111111111111</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2879</v>
+      </c>
+      <c r="B40">
+        <v>47.983333333333334</v>
+      </c>
+      <c r="C40">
+        <v>0.79972222222222222</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>15991</v>
+      </c>
+      <c r="B41">
+        <v>266.51666666666665</v>
+      </c>
+      <c r="C41">
+        <v>4.4419444444444443</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>13533</v>
+      </c>
+      <c r="B42">
+        <v>225.55</v>
+      </c>
+      <c r="C42">
+        <v>3.7591666666666668</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>3040</v>
+      </c>
+      <c r="B43">
+        <v>50.666666666666664</v>
+      </c>
+      <c r="C43">
+        <v>0.84444444444444444</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>10768</v>
+      </c>
+      <c r="B44">
+        <v>179.46666666666667</v>
+      </c>
+      <c r="C44">
+        <v>2.9911111111111111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>4817</v>
+      </c>
+      <c r="B45">
+        <v>80.283333333333331</v>
+      </c>
+      <c r="C45">
+        <v>1.3380555555555556</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>8986</v>
+      </c>
+      <c r="B46">
+        <v>149.76666666666668</v>
+      </c>
+      <c r="C46">
+        <v>2.4961111111111109</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>4026</v>
+      </c>
+      <c r="B47">
+        <v>67.099999999999994</v>
+      </c>
+      <c r="C47">
+        <v>1.1183333333333334</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>1759</v>
+      </c>
+      <c r="B48">
+        <v>29.316666666666666</v>
+      </c>
+      <c r="C48">
+        <v>0.48861111111111111</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>10060</v>
+      </c>
+      <c r="B49">
+        <v>167.66666666666666</v>
+      </c>
+      <c r="C49">
+        <v>2.7944444444444443</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>3175</v>
+      </c>
+      <c r="B50">
+        <v>52.916666666666664</v>
+      </c>
+      <c r="C50">
+        <v>0.88194444444444442</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>3427</v>
+      </c>
+      <c r="B51">
+        <v>57.116666666666667</v>
+      </c>
+      <c r="C51">
+        <v>0.95194444444444448</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63B6A8E3-D8EB-4280-840A-346B01586132}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -841,7 +1627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{700FFB42-EFD7-42BC-9D1E-3691939013EC}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Experiment 1/Time_for_Bac_Fix_Pos50_Start.xlsx
+++ b/Experiment 1/Time_for_Bac_Fix_Pos50_Start.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Experiment 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B14A23E-9EC9-40E6-B8F6-ACEFAA4C0BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB70296-C5FF-4770-BC9D-203F58515185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="18675" windowHeight="12975" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
   </bookViews>
   <sheets>
     <sheet name="All Time Distributions" sheetId="2" r:id="rId1"/>
     <sheet name="Normal Equation" sheetId="4" r:id="rId2"/>
     <sheet name="No Conj" sheetId="1" r:id="rId3"/>
-    <sheet name="No R_a No Conj" sheetId="3" r:id="rId4"/>
+    <sheet name="No R_a with Conj" sheetId="5" r:id="rId4"/>
+    <sheet name="No R_a No Conj" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
   <si>
     <t>Time_s</t>
   </si>
@@ -439,6 +440,9 @@
       <c r="B2">
         <v>8389</v>
       </c>
+      <c r="C2">
+        <v>11341</v>
+      </c>
       <c r="D2">
         <v>4639</v>
       </c>
@@ -450,6 +454,9 @@
       <c r="B3">
         <v>10295</v>
       </c>
+      <c r="C3">
+        <v>4598</v>
+      </c>
       <c r="D3">
         <v>5957</v>
       </c>
@@ -461,6 +468,9 @@
       <c r="B4">
         <v>3898</v>
       </c>
+      <c r="C4">
+        <v>4262</v>
+      </c>
       <c r="D4">
         <v>10392</v>
       </c>
@@ -472,6 +482,9 @@
       <c r="B5">
         <v>6651</v>
       </c>
+      <c r="C5">
+        <v>4249</v>
+      </c>
       <c r="D5">
         <v>7612</v>
       </c>
@@ -483,6 +496,9 @@
       <c r="B6">
         <v>6044</v>
       </c>
+      <c r="C6">
+        <v>6387</v>
+      </c>
       <c r="D6">
         <v>11958</v>
       </c>
@@ -494,6 +510,9 @@
       <c r="B7">
         <v>8004</v>
       </c>
+      <c r="C7">
+        <v>4490</v>
+      </c>
       <c r="D7">
         <v>7537</v>
       </c>
@@ -505,6 +524,9 @@
       <c r="B8">
         <v>20570</v>
       </c>
+      <c r="C8">
+        <v>5991</v>
+      </c>
       <c r="D8">
         <v>5337</v>
       </c>
@@ -516,6 +538,9 @@
       <c r="B9">
         <v>1975</v>
       </c>
+      <c r="C9">
+        <v>3756</v>
+      </c>
       <c r="D9">
         <v>9323</v>
       </c>
@@ -527,6 +552,9 @@
       <c r="B10">
         <v>8326</v>
       </c>
+      <c r="C10">
+        <v>6672</v>
+      </c>
       <c r="D10">
         <v>12175</v>
       </c>
@@ -538,6 +566,9 @@
       <c r="B11">
         <v>8002</v>
       </c>
+      <c r="C11">
+        <v>5460</v>
+      </c>
       <c r="D11">
         <v>6623</v>
       </c>
@@ -549,6 +580,9 @@
       <c r="B12">
         <v>4867</v>
       </c>
+      <c r="C12">
+        <v>7785</v>
+      </c>
       <c r="D12">
         <v>6322</v>
       </c>
@@ -560,6 +594,9 @@
       <c r="B13">
         <v>17082</v>
       </c>
+      <c r="C13">
+        <v>3440</v>
+      </c>
       <c r="D13">
         <v>7208</v>
       </c>
@@ -571,6 +608,9 @@
       <c r="B14">
         <v>5334</v>
       </c>
+      <c r="C14">
+        <v>6852</v>
+      </c>
       <c r="D14">
         <v>13580</v>
       </c>
@@ -582,6 +622,9 @@
       <c r="B15">
         <v>5393</v>
       </c>
+      <c r="C15">
+        <v>6724</v>
+      </c>
       <c r="D15">
         <v>19290</v>
       </c>
@@ -593,6 +636,9 @@
       <c r="B16">
         <v>3162</v>
       </c>
+      <c r="C16">
+        <v>3857</v>
+      </c>
       <c r="D16">
         <v>1009</v>
       </c>
@@ -604,6 +650,9 @@
       <c r="B17">
         <v>2466</v>
       </c>
+      <c r="C17">
+        <v>8556</v>
+      </c>
       <c r="D17">
         <v>4210</v>
       </c>
@@ -615,6 +664,9 @@
       <c r="B18">
         <v>15678</v>
       </c>
+      <c r="C18">
+        <v>3520</v>
+      </c>
       <c r="D18">
         <v>4652</v>
       </c>
@@ -626,6 +678,9 @@
       <c r="B19">
         <v>5932</v>
       </c>
+      <c r="C19">
+        <v>7609</v>
+      </c>
       <c r="D19">
         <v>5145</v>
       </c>
@@ -637,6 +692,9 @@
       <c r="B20">
         <v>2315</v>
       </c>
+      <c r="C20">
+        <v>4536</v>
+      </c>
       <c r="D20">
         <v>4870</v>
       </c>
@@ -647,6 +705,9 @@
       </c>
       <c r="B21">
         <v>1351</v>
+      </c>
+      <c r="C21">
+        <v>2927</v>
       </c>
       <c r="D21">
         <v>4288</v>
@@ -1628,6 +1689,251 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7B78790-86BB-4A67-A9C4-9289D98D0CB3}">
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>11341</v>
+      </c>
+      <c r="B2">
+        <v>189.01666666666668</v>
+      </c>
+      <c r="C2">
+        <v>3.1502777777777777</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>4598</v>
+      </c>
+      <c r="B3">
+        <v>76.63333333333334</v>
+      </c>
+      <c r="C3">
+        <v>1.2772222222222223</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>4262</v>
+      </c>
+      <c r="B4">
+        <v>71.033333333333331</v>
+      </c>
+      <c r="C4">
+        <v>1.183888888888889</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4249</v>
+      </c>
+      <c r="B5">
+        <v>70.816666666666663</v>
+      </c>
+      <c r="C5">
+        <v>1.1802777777777778</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>6387</v>
+      </c>
+      <c r="B6">
+        <v>106.45</v>
+      </c>
+      <c r="C6">
+        <v>1.7741666666666667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>4490</v>
+      </c>
+      <c r="B7">
+        <v>74.833333333333329</v>
+      </c>
+      <c r="C7">
+        <v>1.2472222222222222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>5991</v>
+      </c>
+      <c r="B8">
+        <v>99.85</v>
+      </c>
+      <c r="C8">
+        <v>1.6641666666666666</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>3756</v>
+      </c>
+      <c r="B9">
+        <v>62.6</v>
+      </c>
+      <c r="C9">
+        <v>1.0433333333333332</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>6672</v>
+      </c>
+      <c r="B10">
+        <v>111.2</v>
+      </c>
+      <c r="C10">
+        <v>1.8533333333333333</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>5460</v>
+      </c>
+      <c r="B11">
+        <v>91</v>
+      </c>
+      <c r="C11">
+        <v>1.5166666666666666</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>7785</v>
+      </c>
+      <c r="B12">
+        <v>129.75</v>
+      </c>
+      <c r="C12">
+        <v>2.1625000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>3440</v>
+      </c>
+      <c r="B13">
+        <v>57.333333333333336</v>
+      </c>
+      <c r="C13">
+        <v>0.9555555555555556</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>6852</v>
+      </c>
+      <c r="B14">
+        <v>114.2</v>
+      </c>
+      <c r="C14">
+        <v>1.9033333333333333</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>6724</v>
+      </c>
+      <c r="B15">
+        <v>112.06666666666666</v>
+      </c>
+      <c r="C15">
+        <v>1.8677777777777778</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>3857</v>
+      </c>
+      <c r="B16">
+        <v>64.283333333333331</v>
+      </c>
+      <c r="C16">
+        <v>1.0713888888888889</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>8556</v>
+      </c>
+      <c r="B17">
+        <v>142.6</v>
+      </c>
+      <c r="C17">
+        <v>2.3766666666666665</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>3520</v>
+      </c>
+      <c r="B18">
+        <v>58.666666666666664</v>
+      </c>
+      <c r="C18">
+        <v>0.97777777777777775</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>7609</v>
+      </c>
+      <c r="B19">
+        <v>126.81666666666666</v>
+      </c>
+      <c r="C19">
+        <v>2.1136111111111111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>4536</v>
+      </c>
+      <c r="B20">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="C20">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>2927</v>
+      </c>
+      <c r="B21">
+        <v>48.783333333333331</v>
+      </c>
+      <c r="C21">
+        <v>0.81305555555555553</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{700FFB42-EFD7-42BC-9D1E-3691939013EC}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Experiment 1/Time_for_Bac_Fix_Pos50_Start.xlsx
+++ b/Experiment 1/Time_for_Bac_Fix_Pos50_Start.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Experiment 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB70296-C5FF-4770-BC9D-203F58515185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F2B985-AF6E-45E9-A9C9-FD5336B87FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
   </bookViews>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E58A8867-CC7B-4A27-95B2-91AB61F5580A}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
@@ -717,150 +717,490 @@
       <c r="A22">
         <v>17146</v>
       </c>
+      <c r="C22">
+        <v>12435</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>3574</v>
       </c>
+      <c r="C23">
+        <v>5386</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>4616</v>
       </c>
+      <c r="C24">
+        <v>9049</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>6972</v>
       </c>
+      <c r="C25">
+        <v>2376</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>19492</v>
       </c>
+      <c r="C26">
+        <v>12257</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>14856</v>
       </c>
+      <c r="C27">
+        <v>5748</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>7890</v>
       </c>
+      <c r="C28">
+        <v>12331</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>5025</v>
       </c>
+      <c r="C29">
+        <v>10036</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29157</v>
       </c>
+      <c r="C30">
+        <v>9310</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>6848</v>
       </c>
+      <c r="C31">
+        <v>4006</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>8353</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C32">
+        <v>14518</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>7072</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C33">
+        <v>3385</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>5740</v>
       </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C34">
+        <v>5868</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>4602</v>
       </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C35">
+        <v>7438</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>3289</v>
       </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C36">
+        <v>9594</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>3033</v>
       </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C37">
+        <v>8567</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>4978</v>
       </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C38">
+        <v>6311</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>6970</v>
       </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C39">
+        <v>4121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2879</v>
       </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C40">
+        <v>6181</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>15991</v>
       </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C41">
+        <v>9172</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>13533</v>
       </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C42">
+        <v>9207</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>3040</v>
       </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C43">
+        <v>3832</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>10768</v>
       </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C44">
+        <v>10749</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>4817</v>
       </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C45">
+        <v>6978</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>8986</v>
       </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C46">
+        <v>5663</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>4026</v>
       </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C47">
+        <v>8190</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>1759</v>
       </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C48">
+        <v>5191</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>10060</v>
       </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C49">
+        <v>6559</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>3175</v>
       </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C50">
+        <v>8167</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>3427</v>
+      </c>
+      <c r="C51">
+        <v>3387</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C52">
+        <v>12188</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C53">
+        <v>9785</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C54">
+        <v>7826</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C55">
+        <v>11403</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C56">
+        <v>6329</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C57">
+        <v>12519</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C58">
+        <v>6119</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C59">
+        <v>4847</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C60">
+        <v>8044</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C61">
+        <v>8549</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C62">
+        <v>4180</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C63">
+        <v>8073</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C64">
+        <v>6641</v>
+      </c>
+    </row>
+    <row r="65" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C65">
+        <v>7877</v>
+      </c>
+    </row>
+    <row r="66" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C66">
+        <v>3452</v>
+      </c>
+    </row>
+    <row r="67" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C67">
+        <v>6449</v>
+      </c>
+    </row>
+    <row r="68" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C68">
+        <v>18508</v>
+      </c>
+    </row>
+    <row r="69" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C69">
+        <v>6671</v>
+      </c>
+    </row>
+    <row r="70" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C70">
+        <v>7583</v>
+      </c>
+    </row>
+    <row r="71" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C71">
+        <v>11036</v>
+      </c>
+    </row>
+    <row r="72" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C72">
+        <v>5823</v>
+      </c>
+    </row>
+    <row r="73" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C73">
+        <v>7327</v>
+      </c>
+    </row>
+    <row r="74" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C74">
+        <v>9272</v>
+      </c>
+    </row>
+    <row r="75" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C75">
+        <v>8632</v>
+      </c>
+    </row>
+    <row r="76" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C76">
+        <v>4734</v>
+      </c>
+    </row>
+    <row r="77" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C77">
+        <v>3527</v>
+      </c>
+    </row>
+    <row r="78" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C78">
+        <v>12020</v>
+      </c>
+    </row>
+    <row r="79" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C79">
+        <v>3103</v>
+      </c>
+    </row>
+    <row r="80" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C80">
+        <v>2875</v>
+      </c>
+    </row>
+    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C81">
+        <v>4935</v>
+      </c>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C82">
+        <v>8255</v>
+      </c>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C83">
+        <v>9091</v>
+      </c>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C84">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C85">
+        <v>7603</v>
+      </c>
+    </row>
+    <row r="86" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C86">
+        <v>11051</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C87">
+        <v>9702</v>
+      </c>
+    </row>
+    <row r="88" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C88">
+        <v>4779</v>
+      </c>
+    </row>
+    <row r="89" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C89">
+        <v>10282</v>
+      </c>
+    </row>
+    <row r="90" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C90">
+        <v>5821</v>
+      </c>
+    </row>
+    <row r="91" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C91">
+        <v>2838</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C92">
+        <v>5774</v>
+      </c>
+    </row>
+    <row r="93" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C93">
+        <v>4459</v>
+      </c>
+    </row>
+    <row r="94" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C94">
+        <v>12751</v>
+      </c>
+    </row>
+    <row r="95" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C95">
+        <v>9112</v>
+      </c>
+    </row>
+    <row r="96" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C96">
+        <v>3195</v>
+      </c>
+    </row>
+    <row r="97" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C97">
+        <v>10847</v>
+      </c>
+    </row>
+    <row r="98" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C98">
+        <v>4461</v>
+      </c>
+    </row>
+    <row r="99" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C99">
+        <v>6213</v>
+      </c>
+    </row>
+    <row r="100" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C100">
+        <v>6171</v>
+      </c>
+    </row>
+    <row r="101" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C101">
+        <v>5529</v>
       </c>
     </row>
   </sheetData>
@@ -1690,7 +2030,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7B78790-86BB-4A67-A9C4-9289D98D0CB3}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -1926,6 +2266,886 @@
       </c>
       <c r="C21">
         <v>0.81305555555555553</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>12435</v>
+      </c>
+      <c r="B22">
+        <v>207.25</v>
+      </c>
+      <c r="C22">
+        <v>3.4541666666666666</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>5386</v>
+      </c>
+      <c r="B23">
+        <v>89.766666666666666</v>
+      </c>
+      <c r="C23">
+        <v>1.4961111111111112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>9049</v>
+      </c>
+      <c r="B24">
+        <v>150.81666666666666</v>
+      </c>
+      <c r="C24">
+        <v>2.513611111111111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2376</v>
+      </c>
+      <c r="B25">
+        <v>39.6</v>
+      </c>
+      <c r="C25">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>12257</v>
+      </c>
+      <c r="B26">
+        <v>204.28333333333333</v>
+      </c>
+      <c r="C26">
+        <v>3.4047222222222224</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>5748</v>
+      </c>
+      <c r="B27">
+        <v>95.8</v>
+      </c>
+      <c r="C27">
+        <v>1.5966666666666667</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>12331</v>
+      </c>
+      <c r="B28">
+        <v>205.51666666666668</v>
+      </c>
+      <c r="C28">
+        <v>3.4252777777777776</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>10036</v>
+      </c>
+      <c r="B29">
+        <v>167.26666666666668</v>
+      </c>
+      <c r="C29">
+        <v>2.7877777777777779</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>9310</v>
+      </c>
+      <c r="B30">
+        <v>155.16666666666666</v>
+      </c>
+      <c r="C30">
+        <v>2.5861111111111112</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>4006</v>
+      </c>
+      <c r="B31">
+        <v>66.766666666666666</v>
+      </c>
+      <c r="C31">
+        <v>1.1127777777777779</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>14518</v>
+      </c>
+      <c r="B32">
+        <v>241.96666666666667</v>
+      </c>
+      <c r="C32">
+        <v>4.0327777777777776</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>3385</v>
+      </c>
+      <c r="B33">
+        <v>56.416666666666664</v>
+      </c>
+      <c r="C33">
+        <v>0.94027777777777777</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>5868</v>
+      </c>
+      <c r="B34">
+        <v>97.8</v>
+      </c>
+      <c r="C34">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>7438</v>
+      </c>
+      <c r="B35">
+        <v>123.96666666666667</v>
+      </c>
+      <c r="C35">
+        <v>2.0661111111111112</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>9594</v>
+      </c>
+      <c r="B36">
+        <v>159.9</v>
+      </c>
+      <c r="C36">
+        <v>2.665</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>8567</v>
+      </c>
+      <c r="B37">
+        <v>142.78333333333333</v>
+      </c>
+      <c r="C37">
+        <v>2.3797222222222221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>6311</v>
+      </c>
+      <c r="B38">
+        <v>105.18333333333334</v>
+      </c>
+      <c r="C38">
+        <v>1.7530555555555556</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>4121</v>
+      </c>
+      <c r="B39">
+        <v>68.683333333333337</v>
+      </c>
+      <c r="C39">
+        <v>1.1447222222222222</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>6181</v>
+      </c>
+      <c r="B40">
+        <v>103.01666666666667</v>
+      </c>
+      <c r="C40">
+        <v>1.7169444444444444</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>9172</v>
+      </c>
+      <c r="B41">
+        <v>152.86666666666667</v>
+      </c>
+      <c r="C41">
+        <v>2.5477777777777777</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>9207</v>
+      </c>
+      <c r="B42">
+        <v>153.44999999999999</v>
+      </c>
+      <c r="C42">
+        <v>2.5575000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>3832</v>
+      </c>
+      <c r="B43">
+        <v>63.866666666666667</v>
+      </c>
+      <c r="C43">
+        <v>1.0644444444444445</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>10749</v>
+      </c>
+      <c r="B44">
+        <v>179.15</v>
+      </c>
+      <c r="C44">
+        <v>2.9858333333333333</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>6978</v>
+      </c>
+      <c r="B45">
+        <v>116.3</v>
+      </c>
+      <c r="C45">
+        <v>1.9383333333333332</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>5663</v>
+      </c>
+      <c r="B46">
+        <v>94.38333333333334</v>
+      </c>
+      <c r="C46">
+        <v>1.5730555555555557</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>8190</v>
+      </c>
+      <c r="B47">
+        <v>136.5</v>
+      </c>
+      <c r="C47">
+        <v>2.2749999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>5191</v>
+      </c>
+      <c r="B48">
+        <v>86.516666666666666</v>
+      </c>
+      <c r="C48">
+        <v>1.4419444444444445</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>6559</v>
+      </c>
+      <c r="B49">
+        <v>109.31666666666666</v>
+      </c>
+      <c r="C49">
+        <v>1.8219444444444444</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>8167</v>
+      </c>
+      <c r="B50">
+        <v>136.11666666666667</v>
+      </c>
+      <c r="C50">
+        <v>2.2686111111111109</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>3387</v>
+      </c>
+      <c r="B51">
+        <v>56.45</v>
+      </c>
+      <c r="C51">
+        <v>0.9408333333333333</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>12188</v>
+      </c>
+      <c r="B52">
+        <v>203.13333333333333</v>
+      </c>
+      <c r="C52">
+        <v>3.3855555555555554</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>9785</v>
+      </c>
+      <c r="B53">
+        <v>163.08333333333334</v>
+      </c>
+      <c r="C53">
+        <v>2.7180555555555554</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>7826</v>
+      </c>
+      <c r="B54">
+        <v>130.43333333333334</v>
+      </c>
+      <c r="C54">
+        <v>2.173888888888889</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>11403</v>
+      </c>
+      <c r="B55">
+        <v>190.05</v>
+      </c>
+      <c r="C55">
+        <v>3.1675</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>6329</v>
+      </c>
+      <c r="B56">
+        <v>105.48333333333333</v>
+      </c>
+      <c r="C56">
+        <v>1.7580555555555555</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>12519</v>
+      </c>
+      <c r="B57">
+        <v>208.65</v>
+      </c>
+      <c r="C57">
+        <v>3.4775</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>6119</v>
+      </c>
+      <c r="B58">
+        <v>101.98333333333333</v>
+      </c>
+      <c r="C58">
+        <v>1.6997222222222221</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>4847</v>
+      </c>
+      <c r="B59">
+        <v>80.783333333333331</v>
+      </c>
+      <c r="C59">
+        <v>1.3463888888888889</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>8044</v>
+      </c>
+      <c r="B60">
+        <v>134.06666666666666</v>
+      </c>
+      <c r="C60">
+        <v>2.2344444444444442</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>8549</v>
+      </c>
+      <c r="B61">
+        <v>142.48333333333332</v>
+      </c>
+      <c r="C61">
+        <v>2.3747222222222222</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>4180</v>
+      </c>
+      <c r="B62">
+        <v>69.666666666666671</v>
+      </c>
+      <c r="C62">
+        <v>1.1611111111111112</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>8073</v>
+      </c>
+      <c r="B63">
+        <v>134.55000000000001</v>
+      </c>
+      <c r="C63">
+        <v>2.2425000000000002</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>6641</v>
+      </c>
+      <c r="B64">
+        <v>110.68333333333334</v>
+      </c>
+      <c r="C64">
+        <v>1.8447222222222222</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>7877</v>
+      </c>
+      <c r="B65">
+        <v>131.28333333333333</v>
+      </c>
+      <c r="C65">
+        <v>2.1880555555555556</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>3452</v>
+      </c>
+      <c r="B66">
+        <v>57.533333333333331</v>
+      </c>
+      <c r="C66">
+        <v>0.9588888888888889</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>6449</v>
+      </c>
+      <c r="B67">
+        <v>107.48333333333333</v>
+      </c>
+      <c r="C67">
+        <v>1.7913888888888889</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>18508</v>
+      </c>
+      <c r="B68">
+        <v>308.46666666666664</v>
+      </c>
+      <c r="C68">
+        <v>5.141111111111111</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>6671</v>
+      </c>
+      <c r="B69">
+        <v>111.18333333333334</v>
+      </c>
+      <c r="C69">
+        <v>1.8530555555555555</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>7583</v>
+      </c>
+      <c r="B70">
+        <v>126.38333333333334</v>
+      </c>
+      <c r="C70">
+        <v>2.1063888888888891</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>11036</v>
+      </c>
+      <c r="B71">
+        <v>183.93333333333334</v>
+      </c>
+      <c r="C71">
+        <v>3.0655555555555556</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>5823</v>
+      </c>
+      <c r="B72">
+        <v>97.05</v>
+      </c>
+      <c r="C72">
+        <v>1.6174999999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>7327</v>
+      </c>
+      <c r="B73">
+        <v>122.11666666666666</v>
+      </c>
+      <c r="C73">
+        <v>2.035277777777778</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>9272</v>
+      </c>
+      <c r="B74">
+        <v>154.53333333333333</v>
+      </c>
+      <c r="C74">
+        <v>2.5755555555555554</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>8632</v>
+      </c>
+      <c r="B75">
+        <v>143.86666666666667</v>
+      </c>
+      <c r="C75">
+        <v>2.3977777777777778</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>4734</v>
+      </c>
+      <c r="B76">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="C76">
+        <v>1.3149999999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>3527</v>
+      </c>
+      <c r="B77">
+        <v>58.783333333333331</v>
+      </c>
+      <c r="C77">
+        <v>0.97972222222222227</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>12020</v>
+      </c>
+      <c r="B78">
+        <v>200.33333333333334</v>
+      </c>
+      <c r="C78">
+        <v>3.338888888888889</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>3103</v>
+      </c>
+      <c r="B79">
+        <v>51.716666666666669</v>
+      </c>
+      <c r="C79">
+        <v>0.8619444444444444</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>2875</v>
+      </c>
+      <c r="B80">
+        <v>47.916666666666664</v>
+      </c>
+      <c r="C80">
+        <v>0.79861111111111116</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>4935</v>
+      </c>
+      <c r="B81">
+        <v>82.25</v>
+      </c>
+      <c r="C81">
+        <v>1.3708333333333333</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>8255</v>
+      </c>
+      <c r="B82">
+        <v>137.58333333333334</v>
+      </c>
+      <c r="C82">
+        <v>2.2930555555555556</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>9091</v>
+      </c>
+      <c r="B83">
+        <v>151.51666666666668</v>
+      </c>
+      <c r="C83">
+        <v>2.5252777777777777</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>2120</v>
+      </c>
+      <c r="B84">
+        <v>35.333333333333336</v>
+      </c>
+      <c r="C84">
+        <v>0.58888888888888891</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>7603</v>
+      </c>
+      <c r="B85">
+        <v>126.71666666666667</v>
+      </c>
+      <c r="C85">
+        <v>2.1119444444444446</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>11051</v>
+      </c>
+      <c r="B86">
+        <v>184.18333333333334</v>
+      </c>
+      <c r="C86">
+        <v>3.069722222222222</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>9702</v>
+      </c>
+      <c r="B87">
+        <v>161.69999999999999</v>
+      </c>
+      <c r="C87">
+        <v>2.6949999999999998</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>4779</v>
+      </c>
+      <c r="B88">
+        <v>79.650000000000006</v>
+      </c>
+      <c r="C88">
+        <v>1.3274999999999999</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>10282</v>
+      </c>
+      <c r="B89">
+        <v>171.36666666666667</v>
+      </c>
+      <c r="C89">
+        <v>2.8561111111111113</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>5821</v>
+      </c>
+      <c r="B90">
+        <v>97.016666666666666</v>
+      </c>
+      <c r="C90">
+        <v>1.6169444444444445</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>2838</v>
+      </c>
+      <c r="B91">
+        <v>47.3</v>
+      </c>
+      <c r="C91">
+        <v>0.78833333333333333</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>5774</v>
+      </c>
+      <c r="B92">
+        <v>96.233333333333334</v>
+      </c>
+      <c r="C92">
+        <v>1.6038888888888889</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>4459</v>
+      </c>
+      <c r="B93">
+        <v>74.316666666666663</v>
+      </c>
+      <c r="C93">
+        <v>1.2386111111111111</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>12751</v>
+      </c>
+      <c r="B94">
+        <v>212.51666666666668</v>
+      </c>
+      <c r="C94">
+        <v>3.5419444444444443</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>9112</v>
+      </c>
+      <c r="B95">
+        <v>151.86666666666667</v>
+      </c>
+      <c r="C95">
+        <v>2.5311111111111111</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>3195</v>
+      </c>
+      <c r="B96">
+        <v>53.25</v>
+      </c>
+      <c r="C96">
+        <v>0.88749999999999996</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>10847</v>
+      </c>
+      <c r="B97">
+        <v>180.78333333333333</v>
+      </c>
+      <c r="C97">
+        <v>3.0130555555555554</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>4461</v>
+      </c>
+      <c r="B98">
+        <v>74.349999999999994</v>
+      </c>
+      <c r="C98">
+        <v>1.2391666666666667</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>6213</v>
+      </c>
+      <c r="B99">
+        <v>103.55</v>
+      </c>
+      <c r="C99">
+        <v>1.7258333333333333</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>6171</v>
+      </c>
+      <c r="B100">
+        <v>102.85</v>
+      </c>
+      <c r="C100">
+        <v>1.7141666666666666</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>5529</v>
+      </c>
+      <c r="B101">
+        <v>92.15</v>
+      </c>
+      <c r="C101">
+        <v>1.5358333333333334</v>
       </c>
     </row>
   </sheetData>

--- a/Experiment 1/Time_for_Bac_Fix_Pos50_Start.xlsx
+++ b/Experiment 1/Time_for_Bac_Fix_Pos50_Start.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Moar Documents\GitHub\Bac_Evol_SSA\Experiment 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F2B985-AF6E-45E9-A9C9-FD5336B87FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{399D256D-EAAE-4C82-80B8-D0B7FFE3FECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C5D5DF43-D68A-448F-BEE9-BC751A2734F3}"/>
   </bookViews>
@@ -720,6 +720,9 @@
       <c r="C22">
         <v>12435</v>
       </c>
+      <c r="D22">
+        <v>4423</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
@@ -728,6 +731,9 @@
       <c r="C23">
         <v>5386</v>
       </c>
+      <c r="D23">
+        <v>7000</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
@@ -736,6 +742,9 @@
       <c r="C24">
         <v>9049</v>
       </c>
+      <c r="D24">
+        <v>6444</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
@@ -744,6 +753,9 @@
       <c r="C25">
         <v>2376</v>
       </c>
+      <c r="D25">
+        <v>2517</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
@@ -752,6 +764,9 @@
       <c r="C26">
         <v>12257</v>
       </c>
+      <c r="D26">
+        <v>5061</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
@@ -760,6 +775,9 @@
       <c r="C27">
         <v>5748</v>
       </c>
+      <c r="D27">
+        <v>11865</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
@@ -768,6 +786,9 @@
       <c r="C28">
         <v>12331</v>
       </c>
+      <c r="D28">
+        <v>5506</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
@@ -776,6 +797,9 @@
       <c r="C29">
         <v>10036</v>
       </c>
+      <c r="D29">
+        <v>11084</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
@@ -784,6 +808,9 @@
       <c r="C30">
         <v>9310</v>
       </c>
+      <c r="D30">
+        <v>5880</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
@@ -792,6 +819,9 @@
       <c r="C31">
         <v>4006</v>
       </c>
+      <c r="D31">
+        <v>6383</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
@@ -800,407 +830,617 @@
       <c r="C32">
         <v>14518</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32">
+        <v>5059</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>7072</v>
       </c>
       <c r="C33">
         <v>3385</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33">
+        <v>7720</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>5740</v>
       </c>
       <c r="C34">
         <v>5868</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34">
+        <v>6410</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>4602</v>
       </c>
       <c r="C35">
         <v>7438</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35">
+        <v>6437</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>3289</v>
       </c>
       <c r="C36">
         <v>9594</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36">
+        <v>9239</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>3033</v>
       </c>
       <c r="C37">
         <v>8567</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37">
+        <v>8160</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>4978</v>
       </c>
       <c r="C38">
         <v>6311</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38">
+        <v>5288</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>6970</v>
       </c>
       <c r="C39">
         <v>4121</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39">
+        <v>9524</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2879</v>
       </c>
       <c r="C40">
         <v>6181</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40">
+        <v>9799</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>15991</v>
       </c>
       <c r="C41">
         <v>9172</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41">
+        <v>21687</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>13533</v>
       </c>
       <c r="C42">
         <v>9207</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42">
+        <v>5536</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>3040</v>
       </c>
       <c r="C43">
         <v>3832</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43">
+        <v>5857</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>10768</v>
       </c>
       <c r="C44">
         <v>10749</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44">
+        <v>4332</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>4817</v>
       </c>
       <c r="C45">
         <v>6978</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45">
+        <v>6465</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>8986</v>
       </c>
       <c r="C46">
         <v>5663</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46">
+        <v>5378</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>4026</v>
       </c>
       <c r="C47">
         <v>8190</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47">
+        <v>5090</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>1759</v>
       </c>
       <c r="C48">
         <v>5191</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48">
+        <v>3432</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>10060</v>
       </c>
       <c r="C49">
         <v>6559</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49">
+        <v>7066</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>3175</v>
       </c>
       <c r="C50">
         <v>8167</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50">
+        <v>3738</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>3427</v>
       </c>
       <c r="C51">
         <v>3387</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51">
+        <v>2825</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C52">
         <v>12188</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52">
+        <v>14184</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C53">
         <v>9785</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53">
+        <v>7336</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C54">
         <v>7826</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54">
+        <v>5474</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C55">
         <v>11403</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55">
+        <v>14410</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C56">
         <v>6329</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56">
+        <v>8294</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C57">
         <v>12519</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57">
+        <v>5843</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C58">
         <v>6119</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58">
+        <v>7007</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C59">
         <v>4847</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C60">
         <v>8044</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C61">
         <v>8549</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61">
+        <v>5224</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C62">
         <v>4180</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62">
+        <v>10148</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C63">
         <v>8073</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63">
+        <v>4499</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C64">
         <v>6641</v>
       </c>
-    </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D64">
+        <v>8129</v>
+      </c>
+    </row>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C65">
         <v>7877</v>
       </c>
-    </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D65">
+        <v>5196</v>
+      </c>
+    </row>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C66">
         <v>3452</v>
       </c>
-    </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D66">
+        <v>6901</v>
+      </c>
+    </row>
+    <row r="67" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C67">
         <v>6449</v>
       </c>
-    </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D67">
+        <v>6078</v>
+      </c>
+    </row>
+    <row r="68" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C68">
         <v>18508</v>
       </c>
-    </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D68">
+        <v>5924</v>
+      </c>
+    </row>
+    <row r="69" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C69">
         <v>6671</v>
       </c>
-    </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D69">
+        <v>6478</v>
+      </c>
+    </row>
+    <row r="70" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C70">
         <v>7583</v>
       </c>
-    </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D70">
+        <v>10939</v>
+      </c>
+    </row>
+    <row r="71" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C71">
         <v>11036</v>
       </c>
-    </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D71">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="72" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C72">
         <v>5823</v>
       </c>
-    </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D72">
+        <v>4429</v>
+      </c>
+    </row>
+    <row r="73" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C73">
         <v>7327</v>
       </c>
-    </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D73">
+        <v>9112</v>
+      </c>
+    </row>
+    <row r="74" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C74">
         <v>9272</v>
       </c>
-    </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D74">
+        <v>3061</v>
+      </c>
+    </row>
+    <row r="75" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C75">
         <v>8632</v>
       </c>
-    </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D75">
+        <v>9099</v>
+      </c>
+    </row>
+    <row r="76" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C76">
         <v>4734</v>
       </c>
-    </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D76">
+        <v>3783</v>
+      </c>
+    </row>
+    <row r="77" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C77">
         <v>3527</v>
       </c>
-    </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D77">
+        <v>6506</v>
+      </c>
+    </row>
+    <row r="78" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C78">
         <v>12020</v>
       </c>
-    </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D78">
+        <v>3966</v>
+      </c>
+    </row>
+    <row r="79" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C79">
         <v>3103</v>
       </c>
-    </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D79">
+        <v>5096</v>
+      </c>
+    </row>
+    <row r="80" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C80">
         <v>2875</v>
       </c>
-    </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D80">
+        <v>7606</v>
+      </c>
+    </row>
+    <row r="81" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C81">
         <v>4935</v>
       </c>
-    </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D81">
+        <v>5686</v>
+      </c>
+    </row>
+    <row r="82" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C82">
         <v>8255</v>
       </c>
-    </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D82">
+        <v>4020</v>
+      </c>
+    </row>
+    <row r="83" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C83">
         <v>9091</v>
       </c>
-    </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D83">
+        <v>11361</v>
+      </c>
+    </row>
+    <row r="84" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C84">
         <v>2120</v>
       </c>
-    </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D84">
+        <v>4561</v>
+      </c>
+    </row>
+    <row r="85" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C85">
         <v>7603</v>
       </c>
-    </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D85">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="86" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C86">
         <v>11051</v>
       </c>
-    </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D86">
+        <v>6186</v>
+      </c>
+    </row>
+    <row r="87" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C87">
         <v>9702</v>
       </c>
-    </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D87">
+        <v>9214</v>
+      </c>
+    </row>
+    <row r="88" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C88">
         <v>4779</v>
       </c>
-    </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D88">
+        <v>21398</v>
+      </c>
+    </row>
+    <row r="89" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C89">
         <v>10282</v>
       </c>
-    </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D89">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="90" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C90">
         <v>5821</v>
       </c>
-    </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D90">
+        <v>10996</v>
+      </c>
+    </row>
+    <row r="91" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C91">
         <v>2838</v>
       </c>
-    </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D91">
+        <v>6389</v>
+      </c>
+    </row>
+    <row r="92" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C92">
         <v>5774</v>
       </c>
-    </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D92">
+        <v>9102</v>
+      </c>
+    </row>
+    <row r="93" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C93">
         <v>4459</v>
       </c>
-    </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D93">
+        <v>6428</v>
+      </c>
+    </row>
+    <row r="94" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C94">
         <v>12751</v>
       </c>
-    </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D94">
+        <v>4897</v>
+      </c>
+    </row>
+    <row r="95" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C95">
         <v>9112</v>
       </c>
-    </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D95">
+        <v>4748</v>
+      </c>
+    </row>
+    <row r="96" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C96">
         <v>3195</v>
       </c>
-    </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D96">
+        <v>6942</v>
+      </c>
+    </row>
+    <row r="97" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C97">
         <v>10847</v>
       </c>
-    </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D97">
+        <v>7846</v>
+      </c>
+    </row>
+    <row r="98" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C98">
         <v>4461</v>
       </c>
-    </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D98">
+        <v>10538</v>
+      </c>
+    </row>
+    <row r="99" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C99">
         <v>6213</v>
       </c>
-    </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D99">
+        <v>11893</v>
+      </c>
+    </row>
+    <row r="100" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C100">
         <v>6171</v>
       </c>
-    </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="D100">
+        <v>9233</v>
+      </c>
+    </row>
+    <row r="101" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C101">
         <v>5529</v>
+      </c>
+      <c r="D101">
+        <v>7650</v>
       </c>
     </row>
   </sheetData>
@@ -3155,7 +3395,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{700FFB42-EFD7-42BC-9D1E-3691939013EC}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
@@ -3393,6 +3633,886 @@
         <v>1.191111111111111</v>
       </c>
     </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>4423</v>
+      </c>
+      <c r="B22">
+        <v>73.716666666666669</v>
+      </c>
+      <c r="C22">
+        <v>1.2286111111111111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>7000</v>
+      </c>
+      <c r="B23">
+        <v>116.66666666666667</v>
+      </c>
+      <c r="C23">
+        <v>1.9444444444444444</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>6444</v>
+      </c>
+      <c r="B24">
+        <v>107.4</v>
+      </c>
+      <c r="C24">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2517</v>
+      </c>
+      <c r="B25">
+        <v>41.95</v>
+      </c>
+      <c r="C25">
+        <v>0.69916666666666671</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>5061</v>
+      </c>
+      <c r="B26">
+        <v>84.35</v>
+      </c>
+      <c r="C26">
+        <v>1.4058333333333333</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>11865</v>
+      </c>
+      <c r="B27">
+        <v>197.75</v>
+      </c>
+      <c r="C27">
+        <v>3.2958333333333334</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>5506</v>
+      </c>
+      <c r="B28">
+        <v>91.766666666666666</v>
+      </c>
+      <c r="C28">
+        <v>1.5294444444444444</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>11084</v>
+      </c>
+      <c r="B29">
+        <v>184.73333333333332</v>
+      </c>
+      <c r="C29">
+        <v>3.0788888888888888</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>5880</v>
+      </c>
+      <c r="B30">
+        <v>98</v>
+      </c>
+      <c r="C30">
+        <v>1.6333333333333333</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>6383</v>
+      </c>
+      <c r="B31">
+        <v>106.38333333333334</v>
+      </c>
+      <c r="C31">
+        <v>1.7730555555555556</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>5059</v>
+      </c>
+      <c r="B32">
+        <v>84.316666666666663</v>
+      </c>
+      <c r="C32">
+        <v>1.4052777777777778</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>7720</v>
+      </c>
+      <c r="B33">
+        <v>128.66666666666666</v>
+      </c>
+      <c r="C33">
+        <v>2.1444444444444444</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>6410</v>
+      </c>
+      <c r="B34">
+        <v>106.83333333333333</v>
+      </c>
+      <c r="C34">
+        <v>1.7805555555555554</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>6437</v>
+      </c>
+      <c r="B35">
+        <v>107.28333333333333</v>
+      </c>
+      <c r="C35">
+        <v>1.7880555555555555</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>9239</v>
+      </c>
+      <c r="B36">
+        <v>153.98333333333332</v>
+      </c>
+      <c r="C36">
+        <v>2.5663888888888891</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>8160</v>
+      </c>
+      <c r="B37">
+        <v>136</v>
+      </c>
+      <c r="C37">
+        <v>2.2666666666666666</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>5288</v>
+      </c>
+      <c r="B38">
+        <v>88.13333333333334</v>
+      </c>
+      <c r="C38">
+        <v>1.4688888888888889</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>9524</v>
+      </c>
+      <c r="B39">
+        <v>158.73333333333332</v>
+      </c>
+      <c r="C39">
+        <v>2.6455555555555557</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>9799</v>
+      </c>
+      <c r="B40">
+        <v>163.31666666666666</v>
+      </c>
+      <c r="C40">
+        <v>2.7219444444444445</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>21687</v>
+      </c>
+      <c r="B41">
+        <v>361.45</v>
+      </c>
+      <c r="C41">
+        <v>6.0241666666666669</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>5536</v>
+      </c>
+      <c r="B42">
+        <v>92.266666666666666</v>
+      </c>
+      <c r="C42">
+        <v>1.5377777777777777</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>5857</v>
+      </c>
+      <c r="B43">
+        <v>97.61666666666666</v>
+      </c>
+      <c r="C43">
+        <v>1.6269444444444445</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>4332</v>
+      </c>
+      <c r="B44">
+        <v>72.2</v>
+      </c>
+      <c r="C44">
+        <v>1.2033333333333334</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>6465</v>
+      </c>
+      <c r="B45">
+        <v>107.75</v>
+      </c>
+      <c r="C45">
+        <v>1.7958333333333334</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>5378</v>
+      </c>
+      <c r="B46">
+        <v>89.63333333333334</v>
+      </c>
+      <c r="C46">
+        <v>1.4938888888888888</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>5090</v>
+      </c>
+      <c r="B47">
+        <v>84.833333333333329</v>
+      </c>
+      <c r="C47">
+        <v>1.413888888888889</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>3432</v>
+      </c>
+      <c r="B48">
+        <v>57.2</v>
+      </c>
+      <c r="C48">
+        <v>0.95333333333333337</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>7066</v>
+      </c>
+      <c r="B49">
+        <v>117.76666666666667</v>
+      </c>
+      <c r="C49">
+        <v>1.9627777777777777</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>3738</v>
+      </c>
+      <c r="B50">
+        <v>62.3</v>
+      </c>
+      <c r="C50">
+        <v>1.0383333333333333</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>2825</v>
+      </c>
+      <c r="B51">
+        <v>47.083333333333336</v>
+      </c>
+      <c r="C51">
+        <v>0.78472222222222221</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>14184</v>
+      </c>
+      <c r="B52">
+        <v>236.4</v>
+      </c>
+      <c r="C52">
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>7336</v>
+      </c>
+      <c r="B53">
+        <v>122.26666666666667</v>
+      </c>
+      <c r="C53">
+        <v>2.0377777777777779</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>5474</v>
+      </c>
+      <c r="B54">
+        <v>91.233333333333334</v>
+      </c>
+      <c r="C54">
+        <v>1.5205555555555557</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>14410</v>
+      </c>
+      <c r="B55">
+        <v>240.16666666666666</v>
+      </c>
+      <c r="C55">
+        <v>4.0027777777777782</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>8294</v>
+      </c>
+      <c r="B56">
+        <v>138.23333333333332</v>
+      </c>
+      <c r="C56">
+        <v>2.3038888888888889</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>5843</v>
+      </c>
+      <c r="B57">
+        <v>97.38333333333334</v>
+      </c>
+      <c r="C57">
+        <v>1.6230555555555555</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>7007</v>
+      </c>
+      <c r="B58">
+        <v>116.78333333333333</v>
+      </c>
+      <c r="C58">
+        <v>1.9463888888888889</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>2422</v>
+      </c>
+      <c r="B59">
+        <v>40.366666666666667</v>
+      </c>
+      <c r="C59">
+        <v>0.67277777777777781</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>2143</v>
+      </c>
+      <c r="B60">
+        <v>35.716666666666669</v>
+      </c>
+      <c r="C60">
+        <v>0.59527777777777779</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>5224</v>
+      </c>
+      <c r="B61">
+        <v>87.066666666666663</v>
+      </c>
+      <c r="C61">
+        <v>1.451111111111111</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>10148</v>
+      </c>
+      <c r="B62">
+        <v>169.13333333333333</v>
+      </c>
+      <c r="C62">
+        <v>2.818888888888889</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>4499</v>
+      </c>
+      <c r="B63">
+        <v>74.983333333333334</v>
+      </c>
+      <c r="C63">
+        <v>1.2497222222222222</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>8129</v>
+      </c>
+      <c r="B64">
+        <v>135.48333333333332</v>
+      </c>
+      <c r="C64">
+        <v>2.2580555555555555</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>5196</v>
+      </c>
+      <c r="B65">
+        <v>86.6</v>
+      </c>
+      <c r="C65">
+        <v>1.4433333333333334</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>6901</v>
+      </c>
+      <c r="B66">
+        <v>115.01666666666667</v>
+      </c>
+      <c r="C66">
+        <v>1.9169444444444443</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>6078</v>
+      </c>
+      <c r="B67">
+        <v>101.3</v>
+      </c>
+      <c r="C67">
+        <v>1.6883333333333332</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>5924</v>
+      </c>
+      <c r="B68">
+        <v>98.733333333333334</v>
+      </c>
+      <c r="C68">
+        <v>1.6455555555555557</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>6478</v>
+      </c>
+      <c r="B69">
+        <v>107.96666666666667</v>
+      </c>
+      <c r="C69">
+        <v>1.7994444444444444</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>10939</v>
+      </c>
+      <c r="B70">
+        <v>182.31666666666666</v>
+      </c>
+      <c r="C70">
+        <v>3.0386111111111109</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>2597</v>
+      </c>
+      <c r="B71">
+        <v>43.283333333333331</v>
+      </c>
+      <c r="C71">
+        <v>0.72138888888888886</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>4429</v>
+      </c>
+      <c r="B72">
+        <v>73.816666666666663</v>
+      </c>
+      <c r="C72">
+        <v>1.2302777777777778</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>9112</v>
+      </c>
+      <c r="B73">
+        <v>151.86666666666667</v>
+      </c>
+      <c r="C73">
+        <v>2.5311111111111111</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>3061</v>
+      </c>
+      <c r="B74">
+        <v>51.016666666666666</v>
+      </c>
+      <c r="C74">
+        <v>0.8502777777777778</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>9099</v>
+      </c>
+      <c r="B75">
+        <v>151.65</v>
+      </c>
+      <c r="C75">
+        <v>2.5274999999999999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>3783</v>
+      </c>
+      <c r="B76">
+        <v>63.05</v>
+      </c>
+      <c r="C76">
+        <v>1.0508333333333333</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>6506</v>
+      </c>
+      <c r="B77">
+        <v>108.43333333333334</v>
+      </c>
+      <c r="C77">
+        <v>1.8072222222222223</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>3966</v>
+      </c>
+      <c r="B78">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="C78">
+        <v>1.1016666666666666</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>5096</v>
+      </c>
+      <c r="B79">
+        <v>84.933333333333337</v>
+      </c>
+      <c r="C79">
+        <v>1.4155555555555555</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>7606</v>
+      </c>
+      <c r="B80">
+        <v>126.76666666666667</v>
+      </c>
+      <c r="C80">
+        <v>2.1127777777777776</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>5686</v>
+      </c>
+      <c r="B81">
+        <v>94.766666666666666</v>
+      </c>
+      <c r="C81">
+        <v>1.5794444444444444</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>4020</v>
+      </c>
+      <c r="B82">
+        <v>67</v>
+      </c>
+      <c r="C82">
+        <v>1.1166666666666667</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>11361</v>
+      </c>
+      <c r="B83">
+        <v>189.35</v>
+      </c>
+      <c r="C83">
+        <v>3.1558333333333333</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>4561</v>
+      </c>
+      <c r="B84">
+        <v>76.016666666666666</v>
+      </c>
+      <c r="C84">
+        <v>1.2669444444444444</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>4315</v>
+      </c>
+      <c r="B85">
+        <v>71.916666666666671</v>
+      </c>
+      <c r="C85">
+        <v>1.1986111111111111</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>6186</v>
+      </c>
+      <c r="B86">
+        <v>103.1</v>
+      </c>
+      <c r="C86">
+        <v>1.7183333333333333</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>9214</v>
+      </c>
+      <c r="B87">
+        <v>153.56666666666666</v>
+      </c>
+      <c r="C87">
+        <v>2.5594444444444444</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>21398</v>
+      </c>
+      <c r="B88">
+        <v>356.63333333333333</v>
+      </c>
+      <c r="C88">
+        <v>5.943888888888889</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>1977</v>
+      </c>
+      <c r="B89">
+        <v>32.950000000000003</v>
+      </c>
+      <c r="C89">
+        <v>0.54916666666666669</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>10996</v>
+      </c>
+      <c r="B90">
+        <v>183.26666666666668</v>
+      </c>
+      <c r="C90">
+        <v>3.0544444444444445</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>6389</v>
+      </c>
+      <c r="B91">
+        <v>106.48333333333333</v>
+      </c>
+      <c r="C91">
+        <v>1.7747222222222223</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>9102</v>
+      </c>
+      <c r="B92">
+        <v>151.69999999999999</v>
+      </c>
+      <c r="C92">
+        <v>2.5283333333333333</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>6428</v>
+      </c>
+      <c r="B93">
+        <v>107.13333333333334</v>
+      </c>
+      <c r="C93">
+        <v>1.7855555555555556</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>4897</v>
+      </c>
+      <c r="B94">
+        <v>81.61666666666666</v>
+      </c>
+      <c r="C94">
+        <v>1.3602777777777777</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>4748</v>
+      </c>
+      <c r="B95">
+        <v>79.13333333333334</v>
+      </c>
+      <c r="C95">
+        <v>1.318888888888889</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>6942</v>
+      </c>
+      <c r="B96">
+        <v>115.7</v>
+      </c>
+      <c r="C96">
+        <v>1.9283333333333332</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>7846</v>
+      </c>
+      <c r="B97">
+        <v>130.76666666666668</v>
+      </c>
+      <c r="C97">
+        <v>2.1794444444444445</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>10538</v>
+      </c>
+      <c r="B98">
+        <v>175.63333333333333</v>
+      </c>
+      <c r="C98">
+        <v>2.9272222222222224</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>11893</v>
+      </c>
+      <c r="B99">
+        <v>198.21666666666667</v>
+      </c>
+      <c r="C99">
+        <v>3.3036111111111111</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>9233</v>
+      </c>
+      <c r="B100">
+        <v>153.88333333333333</v>
+      </c>
+      <c r="C100">
+        <v>2.5647222222222221</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>7650</v>
+      </c>
+      <c r="B101">
+        <v>127.5</v>
+      </c>
+      <c r="C101">
+        <v>2.125</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
